--- a/data/학교명_전체.xlsx
+++ b/data/학교명_전체.xlsx
@@ -73123,7 +73123,7 @@
     <row r="2693">
       <c r="A2693" t="inlineStr">
         <is>
-          <t>이화여자대학교사범대학부속이화금란중학교</t>
+          <t>이화여자대학교사범대학부속이화·금란중학교</t>
         </is>
       </c>
       <c r="B2693" t="inlineStr">
